--- a/artfynd/A 50460-2025 artfynd.xlsx
+++ b/artfynd/A 50460-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131303133</v>
       </c>
       <c r="B2" t="n">
-        <v>56456</v>
+        <v>56458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50460-2025 artfynd.xlsx
+++ b/artfynd/A 50460-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131303133</v>
       </c>
       <c r="B2" t="n">
-        <v>56458</v>
+        <v>56459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50460-2025 artfynd.xlsx
+++ b/artfynd/A 50460-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131303133</v>
       </c>
       <c r="B2" t="n">
-        <v>56464</v>
+        <v>56468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50460-2025 artfynd.xlsx
+++ b/artfynd/A 50460-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131303133</v>
       </c>
       <c r="B2" t="n">
-        <v>56468</v>
+        <v>56469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50460-2025 artfynd.xlsx
+++ b/artfynd/A 50460-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131303133</v>
       </c>
       <c r="B2" t="n">
-        <v>56469</v>
+        <v>56472</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50460-2025 artfynd.xlsx
+++ b/artfynd/A 50460-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131303133</v>
       </c>
       <c r="B2" t="n">
-        <v>56472</v>
+        <v>56474</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
